--- a/docs/セキュリティ対応一覧.xlsx
+++ b/docs/セキュリティ対応一覧.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対応一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見送り・残存リスク" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認済み（問題なし）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="対応一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="見送り・残存リスク" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="確認済み（問題なし）" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'対応一覧'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'対応一覧'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>参加申し込みフォームの追加にあたって洗い出したリスクと、その対応状況</t>
+          <t>参加申し込みフォームの追加にあたって洗い出したリスクと、その対応状況。2026-10-21 に、WG への参加・Classroom への招待・サブアプリの分を足した</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-20（2026-10-21 更新）</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>参加申し込みフォーム、メール送信経路、管理者情報の取り扱い</t>
+          <t>参加申し込みフォーム、メール送信経路、管理者情報の取り扱い、WG への参加（Classroom・Chat・GitHub）、サブアプリ（countdown・fe・WG の取り込み）、デプロイの権限</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>本レビューでの指摘と、実施済みの変更（コミット 2021934〜84e0fb3）</t>
+          <t>本レビューでの指摘と、実施済みの変更（コミット 2021934〜84e0fb3）。No.20 以降は 2026-10-21 時点の実装（README・deploy.txt）から</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>COUNTIF(対応一覧!$E$2:$E$20,A11)</f>
+        <f>COUNTIF(対応一覧!$E$2:$E$200,A11)</f>
         <v/>
       </c>
     </row>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>COUNTIF(対応一覧!$E$2:$E$20,A12)</f>
+        <f>COUNTIF(対応一覧!$E$2:$E$200,A12)</f>
         <v/>
       </c>
     </row>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>COUNTA(対応一覧!$A$2:$A$20)</f>
+        <f>COUNTA(対応一覧!$A$2:$A$200)</f>
         <v/>
       </c>
     </row>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B14" s="9">
-        <f>COUNTA('見送り・残存リスク'!$A$2:$A$8)</f>
+        <f>COUNTA('見送り・残存リスク'!$A$2:$A$200)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B15" s="9">
-        <f>COUNTA('確認済み（問題なし）'!$A$2:$A$7)</f>
+        <f>COUNTA('確認済み（問題なし）'!$A$2:$A$200)</f>
         <v/>
       </c>
     </row>
@@ -751,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>自動返信に「心当たりがない場合」の案内を入れ、破棄すれば手続きが進まないと明記</t>
+          <t>自動返信に「心当たりがない場合」の案内を入れ、破棄すれば手続きが進まないと明記。2026-10-20 から、クラスに招待できたときは自動返信を送らない（届くのは Google の招待だけ）</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>本人確認そのものは未実施（確認リンク方式は手間が増えるため見送り）</t>
+          <t>本人確認そのものは未実施（確認リンク方式は手間が増えるため見送り）。他人のアドレスでも、本人が Classroom で「参加」を押さない限りクラスには入らない</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>自由記述（メッセージ欄）を廃止。フォーム項目を固定するテストで復活を防止</t>
+          <t>自由記述（メッセージ欄）を廃止。フォーム項目を固定するテストで復活を防止。2026-10-20 に氏名欄・興味のある WG の欄もなくし、入力はメールアドレスだけにした</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>氏名30文字は依然として攻撃者が制御できる（URLは禁止）</t>
+          <t>—（攻撃者が自動返信に載せられる文字は無くなった）</t>
         </is>
       </c>
     </row>
@@ -912,17 +912,17 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>http / www. / :// を含む氏名を拒否</t>
+          <t>http / www. / :// を含む氏名を拒否 → 2026-10-20 に氏名欄そのものを廃止</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>home/forms.py clean_name</t>
+          <t>home/forms.py</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>氏名欄が無くなったため、対策ごと不要になった</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>ヘッダインジェクション（改行入りの氏名）</t>
+          <t>ヘッダインジェクション（改行入りの入力）</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>インジェクション自体は元から Django が阻止している</t>
+          <t>インジェクション自体は元から Django が阻止している。氏名欄の廃止後は、メールアドレス欄（EmailField の検証あり）だけが対象</t>
         </is>
       </c>
     </row>
@@ -1566,8 +1566,608 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>WG への参加</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>他人のアドレスで、その人がクラブのメンバーかを探られる</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>名簿にいるかどうかが第三者に分かる</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>メンバーでもそうでなくても、画面は同じ「メールを送りました」。結果は本人あてのメールにだけ書く</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/views.py</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>WG への参加</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>本人以外が、他人を WG（Chat・GitHub）に参加させる</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>本人の知らないうちにスペースやチームに入れられる</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>確認のメールのリンクを開いてボタンを押したときだけ追加する（開いただけでは追加しない）。リンクは署名付き・使い捨て・期限1時間（WG_JOIN_LINK_MAX_AGE）</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/verify.py / wgjoin/views.py</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>メールの受信箱を読める人なら手続きを進められる</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>個人情報</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>確認のリンクやアクセスログ、Cookie に大学のアドレスが残る</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>ログの閲覧者や端末の共用者に学籍番号が見える</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>リンクに入れるアドレスと、最後の画面までブラウザに預けるアドレス（Cookie wgjoin_address、HttpOnly・1時間）は SECRET_KEY から作った鍵で暗号化する。DB・セッション・ログには残さない</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/verify.py / wgjoin/views.py</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>SECRET_KEY が漏れると読める</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>フォーム悪用</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>WG への参加の確認メールの送りすぎ</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>第三者あてにメールを繰り返し送らせられる</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>同じ IP は1時間に10件、同じアドレスは1時間に3件まで（WG_JOIN_SEND_LIMITS）。超えたら送らずに断る。アドレスは鍵付きハッシュにして数える。IP の遮断はしない（構内の回線は共有のため）</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/verify.py / config/settings_common.py</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>IP とアドレスの両方を変えれば別勘定になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>認証情報</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>GitHub App（funitclub-wg-join）が org 全体のメンバーを変えられる</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>不具合や悪用で、運営のチームや org の権限を書き換えられる</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>追加できるチームを wg- で始まる名前に限る。すでにいる人はそのまま（maintainer を member に下げない）。GitHub のユーザー名とトークンはその場で使って捨て、ログにも出さない</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/links.py / wgjoin/github.py</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>App の権限（Members: Read and write）自体は org 全体に及ぶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>認証情報</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>運営（クラスの先生）の Google の許可（リフレッシュトークン）</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>漏れると名簿の管理と Chat のメンバー管理を運営の権限で行える</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>スコープは classroom.rosters と chat.memberships だけ。トークンは Key Vault に置く。名簿はアドレスで1人ずつ引き、一覧は取らない</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/google.py / Key Vault: funitclub-kv</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>運営が替わったら取り直す。チャットやリポジトリに貼らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>監視・通知</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Google の許可が切れたときに全員を「メンバーでない」と扱う</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>正規のメンバーが参加できず、原因にも気づけない</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>名簿を引けないときは「名簿を確かめられませんでした」を ERROR で記録し管理者に通知する。Chat に追加できなかったときも、Google が返した status・reason を添えて通知する</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>wgjoin/views.py / wgjoin/google.py</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>通知に載せるのは決まった値だけ（アドレスの入りうる message は載せない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>フォーム悪用</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>参加の申し込みで、他人のアドレスをクラブのクラスに招待させる</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>第三者に Classroom の招待メールが届く</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>もうクラスにいる人には招待しない。招待は運営の承認なしに送るが、本人が「参加」を押さない限りクラスには入らない。送りすぎは参加フォームの連続送信の遮断（No.4）で止まる</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>home/views.py / wgjoin/google.py</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>招待メールそのものは届く</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>個人情報</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>countdown の通知先アドレスを DB に持つ（個人情報を持たない方針の例外）</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>DB が漏れると通知先が読める。ID を知っている人が通知を止めたり差し替えたりできる</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>SECRET_KEY から作った鍵で暗号化して保存し、管理画面にも出さない（登録の有無だけ）。登録は確認のメールのリンクを開いたときだけ。解除と変更は登録したアドレスに届くリンクからだけ</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>works/countdown/crypto.py / works/countdown/views.py</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>SECRET_KEY を替えるときは、前の値を環境変数 SECRET_KEY_FALLBACKS に残す（残さないと全員が未登録の扱い。通知先は暗号化し直さないので、消さずに残す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>アクセス制御</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>countdown の定時送信の入口（/countdown/notify/run/）を外から叩かれる</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>通知を何度も送らせられる</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>合言葉（COUNTDOWN_NOTIFY_TOKEN）を Bearer で照合する（compare_digest）。未設定・不一致は 404。同じ日に何度呼んでも、同じ ID には1通しか送らない</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>works/countdown/views.py</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>アクセス制御</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>FE 対策アプリの問題集の管理（/fe/manage/）を、管理用の ID を言い当てて開かれる</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>全員の問題集を差し替えられる（解答ログも消える）</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>管理用の ID に加えて、編集画面へのログイン（is_staff）を要る条件にした</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>works/fe/views.py AdminRequiredMixin</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>ID には合言葉が無い（成績を見られる・書かれる余地は残る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>情報漏えい</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>非公開の WG のソースが、公開の homepage に入る</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>WG のリポジトリを非公開にしていても、ソースが公開される</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>WG のアプリは homepage にコミットせず、デプロイのときだけ取り込む（wg-apps.yml）。読み取りは Contents: Read だけの GitHub App の短命トークン</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>.github/workflows/deploy.yml / wg-apps.yml</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>デプロイの zip（Actions の成果物、30日）には WG のソースが入る</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>認証情報</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>WG のリポジトリから homepage を書き換えられる</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>WG のメンバーが触れる資格情報で、本番のコードを差し替えられる</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>WG 側に置く App の権限は homepage の Actions: Write（デプロイの起動）だけ。Contents: Write は付けない</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>GitHub App funitclub-wg-deploy</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>デプロイを起動することはできる（中身は homepage の main と wg-apps.yml のまま）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>認証情報</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>GitHub Actions から Azure へのデプロイの資格情報</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>漏れると App Service や同じリソースグループの DB・Key Vault を操作される</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>パスワード・発行プロファイルは使わず OIDC。main ブランチの ID 入りのサブジェクトだけを信頼し、ロールは App Service funITclub スコープの Web サイト共同作成者だけ。SCM の基本認証はオフ</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>マネージド ID funitclub-github-deploy</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>壊れたまま本番に出る（B1 で検証スロットが無い）</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>migrate の失敗などでサイトが落ちたままになる</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>出す前にテストと使い捨て PostgreSQL への migrate、出した後に応答を確かめ、返らなければ直前の zip に戻す</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>.github/workflows/test.yml / deploy.yml</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>WG のアプリ自身のテストは流さない（WG のリポジトリの CI の仕事）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1578,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1711,7 +2311,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>なりすましは防げるが、申し込みの手間が増える</t>
+          <t>なりすましは防げるが、申し込みの手間が増える。WG への参加は確認リンク方式にした（対応一覧 No.21）。申し込みは招待だけで、本人が参加を押さない限り入らないので見送りのまま</t>
         </is>
       </c>
     </row>
@@ -1787,6 +2387,56 @@
       <c r="E8" s="11" t="inlineStr">
         <is>
           <t>ImprovMX 無料枠に送信機能が無いため。相手には学籍番号が伝わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>GitHub App の org 全体の権限</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Members の権限をチーム単位に絞る</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>許容</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>GitHub App の権限にチーム単位の指定が無い。コード側で wg- のチームに限っている（対応一覧 No.24）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>サブアプリの通行証（/works/・/wg/ から辿ったときだけ開く）</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>直打ちで開けないようにする仕組み</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>許容</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>導線の仕掛けで、守りではない。一度入った人のその後は縛らず、Referer も見ない</t>
         </is>
       </c>
     </row>
@@ -1912,7 +2562,7 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>LoginRequiredMiddleware で全ビューが既定ログイン必須。公開ページのみ明示的に除外</t>
+          <t>LoginRequiredMiddleware で全ビューが既定ログイン必須。公開ページ・WG への参加・ログイン不要のサブアプリ（countdown・fe）だけ明示的に除外</t>
         </is>
       </c>
     </row>
